--- a/base_prov/ml/ml_abbott_2026-09-02.xlsx
+++ b/base_prov/ml/ml_abbott_2026-09-02.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\como se me cante\retail-chatbot-main\eci_abbott-main\base_prov\ml\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56480983-35E0-4C04-9DE8-8F566896C0EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADE9A6C2-626A-48E7-B0D5-770E50CB73E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$O$78</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$O$77</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="764" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="701" uniqueCount="173">
   <si>
     <t>fecha</t>
   </si>
@@ -107,12 +107,6 @@
     <t>url_producto</t>
   </si>
   <si>
-    <t>PACK X24 SUPLEMENTO SABOR VAINILLA 237ML NEPRO HP VAINILLA</t>
-  </si>
-  <si>
-    <t>PACK X24 ALIMENTO LOW PROT SABOR VAINILLA NEPRO VAINILLA</t>
-  </si>
-  <si>
     <t>PEDIALYTE NG 12 PACK SABOR COCO 60 MEQ</t>
   </si>
   <si>
@@ -191,9 +185,6 @@
     <t>ENSURE ADVANCE CHOCOLATE – FÓRMULA NUTRICIONAL | PACK 16 PIEZAS DE 237ML</t>
   </si>
   <si>
-    <t>ENSURE ADVANCE FRESA – FÓRMULA NUTRICIONAL | PACK 16 PIEZAS DE 237ML</t>
-  </si>
-  <si>
     <t>ENSURE CLÁSICO CHOCOLATE – FÓRMULA NUTRICIONAL | POLVO 400G</t>
   </si>
   <si>
@@ -203,9 +194,6 @@
     <t>ENSURE ADVANCE CAFÉ – FÓRMULA NUTRICIONAL | PACK 16 PIEZAS DE 237ML</t>
   </si>
   <si>
-    <t>ENSURE PROCARE SUPLEMENTO LÍQUIDO HMB MULTIVITAMÍNICO 30PACK VAINILLA</t>
-  </si>
-  <si>
     <t>SIMILAC ARROZ- ADVANCE FÓRMULA CON HIERRO NO LACTEA PARA LACTANTES CON NECESIDADES ESPECIALES DE NUTRICIÓN 0 A 12 MESES PACK 2 DE 400G</t>
   </si>
   <si>
@@ -227,9 +215,6 @@
     <t>SIMILAC ISOMIL 1 - FÓRMULA NO LACTEA PARA LACTANTES PARA LACTANTES CON NECESIDADES ESPECIALES DE NUTRICIÓN DE 0 A 12 MESES 850G</t>
   </si>
   <si>
-    <t>SIMILAC ETAPA 1 FÓRMULA CON HIERRO PARA LACTANTES DE 0 A 6 MESES 350G</t>
-  </si>
-  <si>
     <t>SIMILAC ARROZ- ADVANCE FÓRMULA CON HIERRO NO LACTEA PARA LACTANTES CON NECESIDADES ESPECIALES DE NUTRICIÓN 0 A 12 MESES 400G</t>
   </si>
   <si>
@@ -278,18 +263,12 @@
     <t>PEDIASURE VAINILLA - ALIMENTACIÓN ESPECIALIZADA PARA NIÑOS DE 1 A 10 AÑOS PACK 24 DE 237 ML</t>
   </si>
   <si>
-    <t>SIMILAC NEOSURE 370GR FÓRMULA CRECIMIENTO BEBÉS PREMATUROS</t>
-  </si>
-  <si>
     <t>PEDIASURE CHOCOLATE - ALIMENTACIÓN ESPECIALIZADA PARA NIÑOS DE 1 A 10 AÑOS PACK 24 DE 237 ML</t>
   </si>
   <si>
     <t>PEDIASURE FRESA - ALIMENTACIÓN ESPECIALIZADA PARA NIÑOS DE 1 A 10 AÑOS PACK 24 DE 237 ML</t>
   </si>
   <si>
-    <t>PEDIASURE VAINILLA- ALIMENTACIÓN ESPECIALIZADA PARA NIÑOS DE 1 A 10 AÑOS  POLVO 400 G</t>
-  </si>
-  <si>
     <t>PEDIASURE FRESA- ALIMENTACIÓN ESPECIALIZADA PARA NIÑOS DE 1 A 10 AÑOS POLVO 400 G</t>
   </si>
   <si>
@@ -302,9 +281,6 @@
     <t>ENSURE ADVANCE CHOCOLATE – FÓRMULA NUTRICIONAL | POLVO 400G</t>
   </si>
   <si>
-    <t>FORMULA PARA ALIMENTACIÓN PROSURE DE 220 ML SABOR VAINILLA</t>
-  </si>
-  <si>
     <t>ENSURE ADVANCE FRESA – FÓRMULA NUTRICIONAL | POLVO 400G</t>
   </si>
   <si>
@@ -329,15 +305,9 @@
     <t>SIMILAC AR - FÓRMULA CON HIERRO A BASE DE ALMIDÓN DE ARROZ PARA LACTANTES CON NECESIDADES ESPECIALES DE NUTRICIÓN 0 A 12 MESES 800G</t>
   </si>
   <si>
-    <t xml:space="preserve">SIMILAC SENSITIVE FÓRMULA CON HIERRO SIN LACTOSA PARA LACTANTES DE 0-12 MESES 350G </t>
-  </si>
-  <si>
     <t xml:space="preserve">SIMILAC SENSITIVE FÓRMULA CON HIERRO SIN LACTOSA PARA LACTANTES DE 0-12 MESES 800G </t>
   </si>
   <si>
-    <t>SIMILAC TOTAL COMFORT 2 FÓRMULA PARA NIÑOS CON NECESIDADES ESPECIALES DE NUTRICIÓN DE 1 A 3 AÑOS 800G</t>
-  </si>
-  <si>
     <t>SIMILAC TOTAL COMFORT ETAPA 1 FÓRMULA PARA LACTANTES DE 0-12 MESES CON NECESIDADES ESPECIALES DE NUTRICIÓN 350G VAINILLA</t>
   </si>
   <si>
@@ -525,6 +495,66 @@
   </si>
   <si>
     <t>2026-09-02</t>
+  </si>
+  <si>
+    <t>ENSURE ADVANCE FRESA FÓRMULA NUTRICIONAL PACK 16 PIEZAS DE 237ML</t>
+  </si>
+  <si>
+    <t>https://www.mercadolibre.com.mx/ensure-advance-fresa-formula-nutricional-pack-16-piezas-de-237ml/p/MLM42482908#polycard_client=search-desktop&amp;be_origin=backend&amp;overlay_label=not_apply&amp;search_layout=grid&amp;position=4&amp;type=product&amp;tracking_id=936e7ea0-7ef8-4053-be55-1dbd319b55d3&amp;wid=MLM6144432216&amp;sid=search</t>
+  </si>
+  <si>
+    <t>ENSURE PROCARE VITAMINAS/MULTIVITAMÍNICOS/MINERALES NUTRICIONAL LÍQUIDO HMB WHEY PROTEIN PACK 30 UNIDADES 220ML VAINILLA</t>
+  </si>
+  <si>
+    <t>https://www.mercadolibre.com.mx/ensure-procare-vitaminasmultivitaminicosminerales-nutricional-liquido-hmb-whey-protein-pack-30-unidades-220ml-vainilla/p/MLM53303424?pdp_filters=official_store%3A178890#polycard_client=search-desktop&amp;be_origin=backend&amp;overlay_label=not_apply&amp;search_layout=grid&amp;position=1&amp;type=product&amp;tracking_id=3b609455-5e54-42c2-87d8-b8245f15b935&amp;wid=MLM3880978850&amp;sid=search</t>
+  </si>
+  <si>
+    <t>FÓRMULA INFANTIL CON HIERRO SIMILAC ETAPA 1 350 GRAMOS N/A</t>
+  </si>
+  <si>
+    <t>https://www.mercadolibre.com.mx/formula-infantil-con-hierro-similac-etapa-1-350-gramos-na/p/MLM30049354#polycard_client=search-desktop&amp;be_origin=backend&amp;overlay_label=not_apply&amp;search_layout=grid&amp;position=2&amp;type=product&amp;tracking_id=66492360-51ef-4b57-9e14-0ae5b5e4fd8d&amp;wid=MLM2004360423&amp;sid=search</t>
+  </si>
+  <si>
+    <t>PACK X24 SUPLEMENTO SABOR VAINILLA 237ML NEPRO HP</t>
+  </si>
+  <si>
+    <t>https://www.mercadolibre.com.mx/pack-x24-suplemento-sabor-vainilla-237ml-nepro-hp/up/MLMU941000822?pdp_filters=item_id:MLM2042277005#intervention_type=MARKET&amp;position=2&amp;search_layout=grid&amp;type=cart_intervention&amp;tracking_id=a49d5436-dcec-4144-b94d-3a81c5d53fe6</t>
+  </si>
+  <si>
+    <t>PACK X24 UNIDADES DE ALIMENTO NEPRO LOW PROT SABOR VAINILLA</t>
+  </si>
+  <si>
+    <t>https://www.mercadolibre.com.mx/pack-x24-unidades-de-alimento-nepro-low-prot-sabor-vainilla/p/MLM35653645?pdp_filters=official_store%3A3897#polycard_client=search-desktop&amp;be_origin=backend&amp;overlay_label=not_apply&amp;search_layout=grid&amp;position=1&amp;type=product&amp;tracking_id=d0edb9b5-2b23-43c1-8e81-02f44bf5554a&amp;wid=MLM2049649453&amp;sid=search</t>
+  </si>
+  <si>
+    <t>https://www.mercadolibre.com.mx/similac-isomil-2-formula-no-lactea-para-ninos-con-necesidades-especiales-de-nutricion-de-1-3-anos-400g/p/MLM15817940#polycard_client=search-desktop&amp;be_origin=backend&amp;overlay_label=not_apply&amp;search_layout=grid&amp;position=2&amp;type=product&amp;tracking_id=b088cdf5-e5fa-4951-add5-5e3e04775707&amp;wid=MLM1431092193&amp;sid=search</t>
+  </si>
+  <si>
+    <t>LECHE NEOSURE BEBES 0 A 12 MESES SIMILAC</t>
+  </si>
+  <si>
+    <t>https://www.mercadolibre.com.mx/leche-neosure-bebes-0-a-12-meses-similac/p/MLM21643181?pdp_filters=official_store%3A179902#polycard_client=search-desktop&amp;be_origin=backend&amp;overlay_label=not_apply&amp;search_layout=grid&amp;position=10&amp;type=product&amp;tracking_id=285afaf3-1f9a-4be0-97d2-39ffb9adc5a4&amp;wid=MLM2243124828&amp;sid=search</t>
+  </si>
+  <si>
+    <t>https://www.mercadolibre.com.mx/pediasure-chocolate-alimentacion-especializada-para-ninos-de-1-a-10-anos-pack-24-de-237-ml/p/MLM45650894#polycard_client=search-desktop&amp;be_origin=backend&amp;overlay_label=not_apply&amp;search_layout=grid&amp;position=1&amp;type=product&amp;tracking_id=59375793-6714-4cdc-9351-2bc1dbbb41bf&amp;wid=MLM2228392203&amp;sid=search</t>
+  </si>
+  <si>
+    <t>PEDIASURE VAINILLA- ALIMENTACIÓN ESPECIALIZADA PARA NIÑOS DE 1 A 10 AÑOS POLVO 400 G</t>
+  </si>
+  <si>
+    <t>https://www.mercadolibre.com.mx/pediasure-vainilla-alimentacion-especializada-para-ninos-de-1-a-10-anos-polvo-400-g/p/MLM19813474#polycard_client=search-desktop&amp;be_origin=backend&amp;overlay_label=not_apply&amp;search_layout=grid&amp;position=1&amp;type=product&amp;tracking_id=9ff6014f-75fc-494b-afb1-d2b596abd0ad&amp;wid=MLM2660884188&amp;sid=search</t>
+  </si>
+  <si>
+    <t>SIMILAC SENSITIVE FÓRMULA CON HIERRO SIN LACTOSA PARA LACTANTES DE 0-12 MESES 350G</t>
+  </si>
+  <si>
+    <t>https://www.mercadolibre.com.mx/similac-sensitive-formula-con-hierro-sin-lactosa-para-lactantes-de-0-12-meses-350g/p/MLM36975278?pdp_filters=official_store%3A179902#polycard_client=search-desktop&amp;be_origin=backend&amp;overlay_label=not_apply&amp;search_layout=grid&amp;position=5&amp;type=product&amp;tracking_id=8eb83f2a-a499-4a5b-91db-31ff5c3721da&amp;wid=MLM2261300037&amp;sid=search</t>
+  </si>
+  <si>
+    <t>SIMILACTOTAL COMFORT 2 FÓRMULA PARA NIÑOS CON NECESIDADES ESPECIALES DE NUTRICIÓN DE 1 A 3 AÑOS 800G</t>
+  </si>
+  <si>
+    <t>https://www.mercadolibre.com.mx/similactotal-comfort-2-formula-para-ninos-con-necesidades-especiales-de-nutricion-de-1-a-3-anos-800g/p/MLM36975275?pdp_filters=official_store%3A179902#polycard_client=search-desktop&amp;be_origin=backend&amp;overlay_label=not_apply&amp;search_layout=grid&amp;position=14&amp;type=product&amp;tracking_id=427e2ff6-e33f-427b-bbec-30fd78295df5&amp;wid=MLM2261261115&amp;sid=search</t>
   </si>
 </sst>
 </file>
@@ -598,7 +628,17 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -907,7 +947,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O78"/>
+  <dimension ref="A1:O77"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.35">
@@ -921,10 +961,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -959,19 +999,19 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="B2" t="s">
         <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D2">
         <v>1344818213</v>
       </c>
       <c r="E2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F2" t="s">
         <v>7</v>
@@ -998,7 +1038,7 @@
         <v>1514</v>
       </c>
       <c r="N2" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="O2" t="s">
         <v>9</v>
@@ -1006,19 +1046,19 @@
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="B3" t="s">
         <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D3">
         <v>2251566859</v>
       </c>
       <c r="E3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F3" t="s">
         <v>7</v>
@@ -1045,7 +1085,7 @@
         <v>1532</v>
       </c>
       <c r="N3" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="O3" t="s">
         <v>9</v>
@@ -1053,19 +1093,19 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="B4" t="s">
         <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D4">
         <v>3537789846</v>
       </c>
       <c r="E4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F4" t="s">
         <v>7</v>
@@ -1092,7 +1132,7 @@
         <v>1077</v>
       </c>
       <c r="N4" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="O4" t="s">
         <v>9</v>
@@ -1100,19 +1140,19 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="B5" t="s">
         <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D5">
         <v>1344811825</v>
       </c>
       <c r="E5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F5" t="s">
         <v>7</v>
@@ -1139,7 +1179,7 @@
         <v>1206</v>
       </c>
       <c r="N5" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="O5" t="s">
         <v>9</v>
@@ -1147,19 +1187,19 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="B6" t="s">
         <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D6">
         <v>53398238</v>
       </c>
       <c r="E6" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F6" t="s">
         <v>7</v>
@@ -1186,7 +1226,7 @@
         <v>1078</v>
       </c>
       <c r="N6" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="O6" t="s">
         <v>9</v>
@@ -1194,19 +1234,19 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="B7" t="s">
         <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D7">
         <v>2372456637</v>
       </c>
       <c r="E7" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F7" t="s">
         <v>7</v>
@@ -1233,7 +1273,7 @@
         <v>1347</v>
       </c>
       <c r="N7" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="O7" t="s">
         <v>9</v>
@@ -1241,19 +1281,19 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="B8" t="s">
         <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D8">
         <v>5336510898</v>
       </c>
       <c r="E8" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F8" t="s">
         <v>7</v>
@@ -1280,7 +1320,7 @@
         <v>1116</v>
       </c>
       <c r="N8" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="O8" t="s">
         <v>9</v>
@@ -1288,19 +1328,19 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="B9" t="s">
         <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D9">
         <v>5336952032</v>
       </c>
       <c r="E9" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F9" t="s">
         <v>7</v>
@@ -1327,7 +1367,7 @@
         <v>1237</v>
       </c>
       <c r="N9" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="O9" t="s">
         <v>9</v>
@@ -1335,19 +1375,19 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="B10" t="s">
         <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D10">
         <v>5336510580</v>
       </c>
       <c r="E10" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F10" t="s">
         <v>7</v>
@@ -1374,7 +1414,7 @@
         <v>1242</v>
       </c>
       <c r="N10" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="O10" t="s">
         <v>9</v>
@@ -1382,19 +1422,19 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="B11" t="s">
         <v>13</v>
       </c>
       <c r="C11" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D11">
         <v>5336510588</v>
       </c>
       <c r="E11" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F11" t="s">
         <v>7</v>
@@ -1421,7 +1461,7 @@
         <v>1241</v>
       </c>
       <c r="N11" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="O11" t="s">
         <v>9</v>
@@ -1429,19 +1469,19 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="B12" t="s">
         <v>13</v>
       </c>
       <c r="C12" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D12">
         <v>2372468319</v>
       </c>
       <c r="E12" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F12" t="s">
         <v>7</v>
@@ -1468,7 +1508,7 @@
         <v>1342</v>
       </c>
       <c r="N12" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="O12" t="s">
         <v>9</v>
@@ -1476,7 +1516,7 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="B13" t="s">
         <v>13</v>
@@ -1488,10 +1528,10 @@
         <v>2853082117</v>
       </c>
       <c r="E13" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F13" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="G13">
         <v>500</v>
@@ -1515,7 +1555,7 @@
         <v>805</v>
       </c>
       <c r="N13" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="O13" t="s">
         <v>11</v>
@@ -1523,19 +1563,19 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="B14" t="s">
         <v>13</v>
       </c>
       <c r="C14" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D14">
         <v>1973439527</v>
       </c>
       <c r="E14" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F14" t="s">
         <v>7</v>
@@ -1562,7 +1602,7 @@
         <v>1947</v>
       </c>
       <c r="N14" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="O14" t="s">
         <v>9</v>
@@ -1570,19 +1610,19 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="B15" t="s">
         <v>13</v>
       </c>
       <c r="C15" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D15">
         <v>2268089725</v>
       </c>
       <c r="E15" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F15" t="s">
         <v>7</v>
@@ -1609,7 +1649,7 @@
         <v>1926</v>
       </c>
       <c r="N15" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="O15" t="s">
         <v>9</v>
@@ -1617,66 +1657,66 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="B16" t="s">
         <v>13</v>
       </c>
       <c r="C16" t="s">
-        <v>51</v>
+        <v>153</v>
       </c>
       <c r="D16">
         <v>3537789844</v>
       </c>
       <c r="E16" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F16" t="s">
-        <v>16</v>
-      </c>
-      <c r="G16" t="s">
-        <v>16</v>
+        <v>7</v>
+      </c>
+      <c r="G16">
+        <v>500</v>
       </c>
       <c r="H16" t="s">
-        <v>16</v>
-      </c>
-      <c r="I16" t="s">
-        <v>16</v>
-      </c>
-      <c r="J16" t="s">
-        <v>16</v>
-      </c>
-      <c r="K16" t="s">
-        <v>16</v>
-      </c>
-      <c r="L16" t="s">
-        <v>16</v>
-      </c>
-      <c r="M16" t="s">
-        <v>16</v>
+        <v>10</v>
+      </c>
+      <c r="I16">
+        <v>43</v>
+      </c>
+      <c r="J16">
+        <v>6</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>64</v>
+      </c>
+      <c r="M16">
+        <v>1912</v>
       </c>
       <c r="N16" t="s">
-        <v>16</v>
+        <v>154</v>
       </c>
       <c r="O16" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="B17" t="s">
         <v>13</v>
       </c>
       <c r="C17" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D17">
         <v>1487393123</v>
       </c>
       <c r="E17" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F17" t="s">
         <v>7</v>
@@ -1703,7 +1743,7 @@
         <v>1970</v>
       </c>
       <c r="N17" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="O17" t="s">
         <v>9</v>
@@ -1711,19 +1751,19 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="B18" t="s">
         <v>13</v>
       </c>
       <c r="C18" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D18">
         <v>1487412130</v>
       </c>
       <c r="E18" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F18" t="s">
         <v>7</v>
@@ -1750,7 +1790,7 @@
         <v>1970</v>
       </c>
       <c r="N18" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="O18" t="s">
         <v>9</v>
@@ -1758,19 +1798,19 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="B19" t="s">
         <v>13</v>
       </c>
       <c r="C19" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D19">
         <v>3537776704</v>
       </c>
       <c r="E19" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F19" t="s">
         <v>7</v>
@@ -1797,7 +1837,7 @@
         <v>1915</v>
       </c>
       <c r="N19" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="O19" t="s">
         <v>9</v>
@@ -1805,66 +1845,66 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="B20" t="s">
         <v>13</v>
       </c>
       <c r="C20" t="s">
-        <v>55</v>
+        <v>155</v>
       </c>
       <c r="D20">
         <v>3880978850</v>
       </c>
       <c r="E20" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F20" t="s">
-        <v>16</v>
-      </c>
-      <c r="G20" t="s">
-        <v>16</v>
+        <v>7</v>
+      </c>
+      <c r="G20">
+        <v>500</v>
       </c>
       <c r="H20" t="s">
-        <v>16</v>
-      </c>
-      <c r="I20" t="s">
-        <v>16</v>
-      </c>
-      <c r="J20" t="s">
-        <v>16</v>
-      </c>
-      <c r="K20" t="s">
-        <v>16</v>
-      </c>
-      <c r="L20" t="s">
-        <v>16</v>
-      </c>
-      <c r="M20" t="s">
-        <v>16</v>
+        <v>12</v>
+      </c>
+      <c r="I20">
+        <v>49</v>
+      </c>
+      <c r="J20">
+        <v>9</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+      <c r="L20">
+        <v>120</v>
+      </c>
+      <c r="M20">
+        <v>1008</v>
       </c>
       <c r="N20" t="s">
-        <v>16</v>
+        <v>156</v>
       </c>
       <c r="O20" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="B21" t="s">
         <v>13</v>
       </c>
       <c r="C21" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D21">
         <v>3866576502</v>
       </c>
       <c r="E21" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F21" t="s">
         <v>7</v>
@@ -1891,7 +1931,7 @@
         <v>862</v>
       </c>
       <c r="N21" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="O21" t="s">
         <v>9</v>
@@ -1899,7 +1939,7 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="B22" t="s">
         <v>13</v>
@@ -1911,7 +1951,7 @@
         <v>2975827632</v>
       </c>
       <c r="E22" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F22" t="s">
         <v>7</v>
@@ -1938,7 +1978,7 @@
         <v>783</v>
       </c>
       <c r="N22" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="O22" t="s">
         <v>9</v>
@@ -1946,19 +1986,19 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="B23" t="s">
         <v>13</v>
       </c>
       <c r="C23" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D23">
         <v>1387013248</v>
       </c>
       <c r="E23" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F23" t="s">
         <v>7</v>
@@ -1985,7 +2025,7 @@
         <v>679</v>
       </c>
       <c r="N23" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="O23" t="s">
         <v>9</v>
@@ -1993,19 +2033,19 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="B24" t="s">
         <v>13</v>
       </c>
       <c r="C24" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D24">
         <v>3833162316</v>
       </c>
       <c r="E24" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F24" t="s">
         <v>7</v>
@@ -2032,7 +2072,7 @@
         <v>679</v>
       </c>
       <c r="N24" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="O24" t="s">
         <v>9</v>
@@ -2040,19 +2080,19 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="B25" t="s">
         <v>13</v>
       </c>
       <c r="C25" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D25">
         <v>3537751334</v>
       </c>
       <c r="E25" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F25" t="s">
         <v>7</v>
@@ -2079,7 +2119,7 @@
         <v>633</v>
       </c>
       <c r="N25" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="O25" t="s">
         <v>9</v>
@@ -2087,19 +2127,19 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="B26" t="s">
         <v>13</v>
       </c>
       <c r="C26" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D26">
         <v>1918678287</v>
       </c>
       <c r="E26" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F26" t="s">
         <v>7</v>
@@ -2126,7 +2166,7 @@
         <v>417</v>
       </c>
       <c r="N26" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="O26" t="s">
         <v>9</v>
@@ -2134,22 +2174,22 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="B27" t="s">
         <v>13</v>
       </c>
       <c r="C27" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D27">
         <v>1344793647</v>
       </c>
       <c r="E27" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F27" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="G27">
         <v>1000</v>
@@ -2173,7 +2213,7 @@
         <v>427</v>
       </c>
       <c r="N27" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="O27" t="s">
         <v>11</v>
@@ -2181,22 +2221,22 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="B28" t="s">
         <v>13</v>
       </c>
       <c r="C28" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D28">
         <v>1344811832</v>
       </c>
       <c r="E28" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F28" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="G28">
         <v>1000</v>
@@ -2220,7 +2260,7 @@
         <v>425</v>
       </c>
       <c r="N28" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="O28" t="s">
         <v>11</v>
@@ -2228,66 +2268,66 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="B29" t="s">
         <v>13</v>
       </c>
       <c r="C29" t="s">
-        <v>63</v>
+        <v>157</v>
       </c>
       <c r="D29">
         <v>2334097590</v>
       </c>
       <c r="E29" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F29" t="s">
-        <v>16</v>
-      </c>
-      <c r="G29" t="s">
-        <v>16</v>
+        <v>7</v>
+      </c>
+      <c r="G29">
+        <v>100</v>
       </c>
       <c r="H29" t="s">
-        <v>16</v>
-      </c>
-      <c r="I29" t="s">
-        <v>16</v>
-      </c>
-      <c r="J29" t="s">
-        <v>16</v>
-      </c>
-      <c r="K29" t="s">
-        <v>16</v>
-      </c>
-      <c r="L29" t="s">
-        <v>16</v>
-      </c>
-      <c r="M29" t="s">
-        <v>16</v>
+        <v>10</v>
+      </c>
+      <c r="I29">
+        <v>946</v>
+      </c>
+      <c r="J29">
+        <v>2</v>
+      </c>
+      <c r="K29">
+        <v>0</v>
+      </c>
+      <c r="L29">
+        <v>58</v>
+      </c>
+      <c r="M29">
+        <v>606</v>
       </c>
       <c r="N29" t="s">
-        <v>16</v>
+        <v>158</v>
       </c>
       <c r="O29" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="B30" t="s">
         <v>13</v>
       </c>
       <c r="C30" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="D30">
         <v>1485136166</v>
       </c>
       <c r="E30" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F30" t="s">
         <v>7</v>
@@ -2314,7 +2354,7 @@
         <v>850</v>
       </c>
       <c r="N30" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="O30" t="s">
         <v>9</v>
@@ -2322,19 +2362,19 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="B31" t="s">
         <v>13</v>
       </c>
       <c r="C31" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D31">
         <v>2975802702</v>
       </c>
       <c r="E31" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F31" t="s">
         <v>7</v>
@@ -2361,7 +2401,7 @@
         <v>1356</v>
       </c>
       <c r="N31" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="O31" t="s">
         <v>9</v>
@@ -2369,66 +2409,66 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="B32" t="s">
         <v>13</v>
       </c>
       <c r="C32" t="s">
-        <v>23</v>
+        <v>159</v>
       </c>
       <c r="D32">
         <v>2042277005</v>
       </c>
       <c r="E32" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F32" t="s">
-        <v>16</v>
-      </c>
-      <c r="G32" t="s">
-        <v>16</v>
+        <v>7</v>
+      </c>
+      <c r="G32">
+        <v>10000</v>
       </c>
       <c r="H32" t="s">
-        <v>16</v>
-      </c>
-      <c r="I32" t="s">
-        <v>16</v>
-      </c>
-      <c r="J32" t="s">
-        <v>16</v>
-      </c>
-      <c r="K32" t="s">
-        <v>16</v>
+        <v>10</v>
+      </c>
+      <c r="I32">
+        <v>44</v>
+      </c>
+      <c r="J32">
+        <v>4</v>
+      </c>
+      <c r="K32">
+        <v>0</v>
       </c>
       <c r="L32">
-        <v>58</v>
-      </c>
-      <c r="M32" t="s">
-        <v>16</v>
+        <v>49</v>
+      </c>
+      <c r="M32">
+        <v>463</v>
       </c>
       <c r="N32" t="s">
-        <v>16</v>
+        <v>160</v>
       </c>
       <c r="O32" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="B33" t="s">
         <v>13</v>
       </c>
       <c r="C33" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="D33">
         <v>3537852808</v>
       </c>
       <c r="E33" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F33" t="s">
         <v>7</v>
@@ -2455,7 +2495,7 @@
         <v>1095</v>
       </c>
       <c r="N33" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="O33" t="s">
         <v>9</v>
@@ -2463,19 +2503,19 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="B34" t="s">
         <v>13</v>
       </c>
       <c r="C34" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="D34">
         <v>1599152042</v>
       </c>
       <c r="E34" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F34" t="s">
         <v>7</v>
@@ -2502,7 +2542,7 @@
         <v>1130</v>
       </c>
       <c r="N34" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="O34" t="s">
         <v>9</v>
@@ -2510,22 +2550,22 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="B35" t="s">
         <v>13</v>
       </c>
       <c r="C35" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="D35">
         <v>3537751314</v>
       </c>
       <c r="E35" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F35" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="G35">
         <v>5000</v>
@@ -2549,7 +2589,7 @@
         <v>1094</v>
       </c>
       <c r="N35" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="O35" t="s">
         <v>11</v>
@@ -2557,19 +2597,19 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="B36" t="s">
         <v>13</v>
       </c>
       <c r="C36" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="D36">
         <v>1599499235</v>
       </c>
       <c r="E36" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F36" t="s">
         <v>7</v>
@@ -2596,7 +2636,7 @@
         <v>1562</v>
       </c>
       <c r="N36" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="O36" t="s">
         <v>9</v>
@@ -2604,19 +2644,19 @@
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="B37" t="s">
         <v>13</v>
       </c>
       <c r="C37" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="D37">
         <v>3537826884</v>
       </c>
       <c r="E37" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F37" t="s">
         <v>7</v>
@@ -2643,7 +2683,7 @@
         <v>1524</v>
       </c>
       <c r="N37" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="O37" t="s">
         <v>9</v>
@@ -2651,19 +2691,19 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="B38" t="s">
         <v>13</v>
       </c>
       <c r="C38" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="D38">
         <v>5078833892</v>
       </c>
       <c r="E38" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F38" t="s">
         <v>16</v>
@@ -2683,8 +2723,8 @@
       <c r="K38" t="s">
         <v>16</v>
       </c>
-      <c r="L38">
-        <v>113</v>
+      <c r="L38" t="s">
+        <v>16</v>
       </c>
       <c r="M38" t="s">
         <v>16</v>
@@ -2698,19 +2738,19 @@
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="B39" t="s">
         <v>13</v>
       </c>
       <c r="C39" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="D39">
         <v>3857885868</v>
       </c>
       <c r="E39" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F39" t="s">
         <v>16</v>
@@ -2730,8 +2770,8 @@
       <c r="K39" t="s">
         <v>16</v>
       </c>
-      <c r="L39">
-        <v>113</v>
+      <c r="L39" t="s">
+        <v>16</v>
       </c>
       <c r="M39" t="s">
         <v>16</v>
@@ -2745,19 +2785,19 @@
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="B40" t="s">
         <v>13</v>
       </c>
       <c r="C40" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="D40">
         <v>2861827737</v>
       </c>
       <c r="E40" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F40" t="s">
         <v>16</v>
@@ -2777,8 +2817,8 @@
       <c r="K40" t="s">
         <v>16</v>
       </c>
-      <c r="L40">
-        <v>99</v>
+      <c r="L40" t="s">
+        <v>16</v>
       </c>
       <c r="M40" t="s">
         <v>16</v>
@@ -2792,66 +2832,66 @@
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="B41" t="s">
         <v>13</v>
       </c>
       <c r="C41" t="s">
-        <v>24</v>
+        <v>161</v>
       </c>
       <c r="D41">
         <v>2035806901</v>
       </c>
       <c r="E41" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F41" t="s">
-        <v>16</v>
-      </c>
-      <c r="G41" t="s">
-        <v>16</v>
+        <v>7</v>
+      </c>
+      <c r="G41">
+        <v>5000</v>
       </c>
       <c r="H41" t="s">
-        <v>16</v>
-      </c>
-      <c r="I41" t="s">
-        <v>16</v>
-      </c>
-      <c r="J41" t="s">
-        <v>16</v>
-      </c>
-      <c r="K41" t="s">
-        <v>16</v>
+        <v>10</v>
+      </c>
+      <c r="I41">
+        <v>445</v>
+      </c>
+      <c r="J41">
+        <v>7</v>
+      </c>
+      <c r="K41">
+        <v>1</v>
       </c>
       <c r="L41">
-        <v>56</v>
-      </c>
-      <c r="M41" t="s">
-        <v>16</v>
+        <v>59</v>
+      </c>
+      <c r="M41">
+        <v>749</v>
       </c>
       <c r="N41" t="s">
-        <v>16</v>
+        <v>162</v>
       </c>
       <c r="O41" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="B42" t="s">
         <v>13</v>
       </c>
       <c r="C42" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="D42">
         <v>2385333737</v>
       </c>
       <c r="E42" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F42" t="s">
         <v>16</v>
@@ -2871,8 +2911,8 @@
       <c r="K42" t="s">
         <v>16</v>
       </c>
-      <c r="L42">
-        <v>56</v>
+      <c r="L42" t="s">
+        <v>16</v>
       </c>
       <c r="M42" t="s">
         <v>16</v>
@@ -2886,19 +2926,19 @@
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="B43" t="s">
         <v>13</v>
       </c>
       <c r="C43" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="D43">
         <v>4784239772</v>
       </c>
       <c r="E43" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F43" t="s">
         <v>16</v>
@@ -2918,8 +2958,8 @@
       <c r="K43" t="s">
         <v>16</v>
       </c>
-      <c r="L43">
-        <v>56</v>
+      <c r="L43" t="s">
+        <v>16</v>
       </c>
       <c r="M43" t="s">
         <v>16</v>
@@ -2933,19 +2973,19 @@
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="B44" t="s">
         <v>13</v>
       </c>
       <c r="C44" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="D44">
         <v>5164338894</v>
       </c>
       <c r="E44" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F44" t="s">
         <v>16</v>
@@ -2965,8 +3005,8 @@
       <c r="K44" t="s">
         <v>16</v>
       </c>
-      <c r="L44">
-        <v>56</v>
+      <c r="L44" t="s">
+        <v>16</v>
       </c>
       <c r="M44" t="s">
         <v>16</v>
@@ -2980,19 +3020,19 @@
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="B45" t="s">
         <v>13</v>
       </c>
       <c r="C45" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D45">
         <v>2981481597</v>
       </c>
       <c r="E45" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F45" t="s">
         <v>7</v>
@@ -3019,7 +3059,7 @@
         <v>796</v>
       </c>
       <c r="N45" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="O45" t="s">
         <v>9</v>
@@ -3027,19 +3067,19 @@
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="B46" t="s">
         <v>13</v>
       </c>
       <c r="C46" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="D46">
         <v>1485178523</v>
       </c>
       <c r="E46" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F46" t="s">
         <v>7</v>
@@ -3066,7 +3106,7 @@
         <v>1974</v>
       </c>
       <c r="N46" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="O46" t="s">
         <v>9</v>
@@ -3074,19 +3114,19 @@
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="B47" t="s">
         <v>13</v>
       </c>
       <c r="C47" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="D47">
         <v>2742594909</v>
       </c>
       <c r="E47" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F47" t="s">
         <v>16</v>
@@ -3106,8 +3146,8 @@
       <c r="K47" t="s">
         <v>16</v>
       </c>
-      <c r="L47">
-        <v>103</v>
+      <c r="L47" t="s">
+        <v>16</v>
       </c>
       <c r="M47" t="s">
         <v>16</v>
@@ -3121,66 +3161,66 @@
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="B48" t="s">
         <v>13</v>
       </c>
       <c r="C48" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="D48">
         <v>1386149008</v>
       </c>
       <c r="E48" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F48" t="s">
-        <v>16</v>
-      </c>
-      <c r="G48" t="s">
-        <v>16</v>
+        <v>7</v>
+      </c>
+      <c r="G48">
+        <v>5000</v>
       </c>
       <c r="H48" t="s">
-        <v>16</v>
-      </c>
-      <c r="I48" t="s">
-        <v>16</v>
-      </c>
-      <c r="J48" t="s">
-        <v>16</v>
-      </c>
-      <c r="K48" t="s">
-        <v>16</v>
+        <v>8</v>
+      </c>
+      <c r="I48">
+        <v>380</v>
+      </c>
+      <c r="J48">
+        <v>6</v>
+      </c>
+      <c r="K48">
+        <v>0</v>
       </c>
       <c r="L48">
         <v>104</v>
       </c>
-      <c r="M48" t="s">
-        <v>16</v>
+      <c r="M48">
+        <v>681</v>
       </c>
       <c r="N48" t="s">
-        <v>16</v>
+        <v>163</v>
       </c>
       <c r="O48" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="B49" t="s">
         <v>13</v>
       </c>
       <c r="C49" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="D49">
         <v>3537814136</v>
       </c>
       <c r="E49" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F49" t="s">
         <v>7</v>
@@ -3207,7 +3247,7 @@
         <v>1343</v>
       </c>
       <c r="N49" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="O49" t="s">
         <v>9</v>
@@ -3215,113 +3255,113 @@
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="B50" t="s">
         <v>13</v>
       </c>
       <c r="C50" t="s">
-        <v>80</v>
+        <v>164</v>
       </c>
       <c r="D50">
         <v>1386166955</v>
       </c>
       <c r="E50" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F50" t="s">
-        <v>16</v>
-      </c>
-      <c r="G50" t="s">
-        <v>16</v>
+        <v>7</v>
+      </c>
+      <c r="G50">
+        <v>5000</v>
       </c>
       <c r="H50" t="s">
-        <v>16</v>
-      </c>
-      <c r="I50" t="s">
-        <v>16</v>
-      </c>
-      <c r="J50" t="s">
-        <v>16</v>
-      </c>
-      <c r="K50" t="s">
-        <v>16</v>
+        <v>10</v>
+      </c>
+      <c r="I50">
+        <v>170</v>
+      </c>
+      <c r="J50">
+        <v>6</v>
+      </c>
+      <c r="K50">
+        <v>0</v>
       </c>
       <c r="L50">
-        <v>58</v>
-      </c>
-      <c r="M50" t="s">
-        <v>16</v>
+        <v>40</v>
+      </c>
+      <c r="M50">
+        <v>450</v>
       </c>
       <c r="N50" t="s">
-        <v>16</v>
+        <v>165</v>
       </c>
       <c r="O50" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="B51" t="s">
         <v>13</v>
       </c>
       <c r="C51" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="D51">
         <v>3537839838</v>
       </c>
       <c r="E51" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F51" t="s">
-        <v>16</v>
-      </c>
-      <c r="G51" t="s">
-        <v>16</v>
+        <v>7</v>
+      </c>
+      <c r="G51">
+        <v>1000</v>
       </c>
       <c r="H51" t="s">
-        <v>16</v>
-      </c>
-      <c r="I51" t="s">
-        <v>16</v>
-      </c>
-      <c r="J51" t="s">
-        <v>16</v>
-      </c>
-      <c r="K51" t="s">
-        <v>16</v>
+        <v>10</v>
+      </c>
+      <c r="I51">
+        <v>673</v>
+      </c>
+      <c r="J51">
+        <v>6</v>
+      </c>
+      <c r="K51">
+        <v>1</v>
       </c>
       <c r="L51">
         <v>92</v>
       </c>
-      <c r="M51" t="s">
-        <v>16</v>
+      <c r="M51">
+        <v>1309</v>
       </c>
       <c r="N51" t="s">
-        <v>16</v>
+        <v>166</v>
       </c>
       <c r="O51" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="B52" t="s">
         <v>13</v>
       </c>
       <c r="C52" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="D52">
         <v>3537826888</v>
       </c>
       <c r="E52" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F52" t="s">
         <v>7</v>
@@ -3348,7 +3388,7 @@
         <v>1305</v>
       </c>
       <c r="N52" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="O52" t="s">
         <v>9</v>
@@ -3356,66 +3396,66 @@
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="B53" t="s">
         <v>13</v>
       </c>
       <c r="C53" t="s">
-        <v>83</v>
+        <v>167</v>
       </c>
       <c r="D53">
         <v>1344836181</v>
       </c>
       <c r="E53" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F53" t="s">
-        <v>16</v>
-      </c>
-      <c r="G53" t="s">
-        <v>16</v>
+        <v>7</v>
+      </c>
+      <c r="G53">
+        <v>5000</v>
       </c>
       <c r="H53" t="s">
-        <v>16</v>
-      </c>
-      <c r="I53" t="s">
-        <v>16</v>
-      </c>
-      <c r="J53" t="s">
-        <v>16</v>
-      </c>
-      <c r="K53" t="s">
-        <v>16</v>
+        <v>10</v>
+      </c>
+      <c r="I53">
+        <v>2474</v>
+      </c>
+      <c r="J53">
+        <v>7</v>
+      </c>
+      <c r="K53">
+        <v>0</v>
       </c>
       <c r="L53">
-        <v>85</v>
-      </c>
-      <c r="M53" t="s">
-        <v>16</v>
+        <v>84</v>
+      </c>
+      <c r="M53">
+        <v>1324</v>
       </c>
       <c r="N53" t="s">
-        <v>16</v>
+        <v>168</v>
       </c>
       <c r="O53" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="B54" t="s">
         <v>13</v>
       </c>
       <c r="C54" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="D54">
         <v>1485178537</v>
       </c>
       <c r="E54" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F54" t="s">
         <v>7</v>
@@ -3442,7 +3482,7 @@
         <v>1202</v>
       </c>
       <c r="N54" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="O54" t="s">
         <v>9</v>
@@ -3450,19 +3490,19 @@
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="B55" t="s">
         <v>13</v>
       </c>
       <c r="C55" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="D55">
         <v>3537738384</v>
       </c>
       <c r="E55" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F55" t="s">
         <v>7</v>
@@ -3489,7 +3529,7 @@
         <v>1923</v>
       </c>
       <c r="N55" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="O55" t="s">
         <v>9</v>
@@ -3497,19 +3537,19 @@
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="B56" t="s">
         <v>13</v>
       </c>
       <c r="C56" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="D56">
         <v>5507380358</v>
       </c>
       <c r="E56" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F56" t="s">
         <v>7</v>
@@ -3536,7 +3576,7 @@
         <v>1078</v>
       </c>
       <c r="N56" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="O56" t="s">
         <v>9</v>
@@ -3544,19 +3584,19 @@
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="B57" t="s">
         <v>13</v>
       </c>
       <c r="C57" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="D57">
         <v>1485123308</v>
       </c>
       <c r="E57" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F57" t="s">
         <v>7</v>
@@ -3583,7 +3623,7 @@
         <v>1948</v>
       </c>
       <c r="N57" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="O57" t="s">
         <v>9</v>
@@ -3591,66 +3631,66 @@
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="B58" t="s">
         <v>13</v>
       </c>
       <c r="C58" t="s">
-        <v>88</v>
+        <v>171</v>
       </c>
       <c r="D58">
         <v>2035712373</v>
       </c>
       <c r="E58" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F58" t="s">
-        <v>16</v>
-      </c>
-      <c r="G58" t="s">
-        <v>16</v>
+        <v>7</v>
+      </c>
+      <c r="G58">
+        <v>500</v>
       </c>
       <c r="H58" t="s">
-        <v>16</v>
-      </c>
-      <c r="I58" t="s">
-        <v>16</v>
-      </c>
-      <c r="J58" t="s">
-        <v>16</v>
-      </c>
-      <c r="K58" t="s">
-        <v>16</v>
+        <v>8</v>
+      </c>
+      <c r="I58">
+        <v>204</v>
+      </c>
+      <c r="J58">
+        <v>6</v>
+      </c>
+      <c r="K58">
+        <v>0</v>
       </c>
       <c r="L58">
-        <v>58</v>
-      </c>
-      <c r="M58" t="s">
-        <v>16</v>
+        <v>100</v>
+      </c>
+      <c r="M58">
+        <v>620</v>
       </c>
       <c r="N58" t="s">
-        <v>16</v>
+        <v>172</v>
       </c>
       <c r="O58" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="B59" t="s">
         <v>13</v>
       </c>
       <c r="C59" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D59">
         <v>2739131393</v>
       </c>
       <c r="E59" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F59" t="s">
         <v>16</v>
@@ -3685,19 +3725,19 @@
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="B60" t="s">
         <v>13</v>
       </c>
       <c r="C60" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="D60">
         <v>1485148997</v>
       </c>
       <c r="E60" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F60" t="s">
         <v>7</v>
@@ -3724,7 +3764,7 @@
         <v>1905</v>
       </c>
       <c r="N60" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="O60" t="s">
         <v>9</v>
@@ -3732,19 +3772,19 @@
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="B61" t="s">
         <v>13</v>
       </c>
       <c r="C61" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="D61">
         <v>2372468289</v>
       </c>
       <c r="E61" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F61" t="s">
         <v>7</v>
@@ -3771,7 +3811,7 @@
         <v>1550</v>
       </c>
       <c r="N61" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="O61" t="s">
         <v>9</v>
@@ -3779,19 +3819,19 @@
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="B62" t="s">
         <v>13</v>
       </c>
       <c r="C62" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="D62">
         <v>1918665431</v>
       </c>
       <c r="E62" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F62" t="s">
         <v>7</v>
@@ -3818,7 +3858,7 @@
         <v>488</v>
       </c>
       <c r="N62" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="O62" t="s">
         <v>9</v>
@@ -3826,19 +3866,19 @@
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="B63" t="s">
         <v>13</v>
       </c>
       <c r="C63" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="D63">
         <v>1918627059</v>
       </c>
       <c r="E63" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F63" t="s">
         <v>16</v>
@@ -3858,8 +3898,8 @@
       <c r="K63" t="s">
         <v>16</v>
       </c>
-      <c r="L63">
-        <v>68</v>
+      <c r="L63" t="s">
+        <v>16</v>
       </c>
       <c r="M63" t="s">
         <v>16</v>
@@ -3873,19 +3913,19 @@
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="B64" t="s">
         <v>13</v>
       </c>
       <c r="C64" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="D64">
         <v>1918627057</v>
       </c>
       <c r="E64" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F64" t="s">
         <v>7</v>
@@ -3912,7 +3952,7 @@
         <v>527</v>
       </c>
       <c r="N64" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="O64" t="s">
         <v>9</v>
@@ -3920,19 +3960,19 @@
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="B65" t="s">
         <v>13</v>
       </c>
       <c r="C65" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="D65">
         <v>2035768243</v>
       </c>
       <c r="E65" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F65" t="s">
         <v>7</v>
@@ -3959,7 +3999,7 @@
         <v>418</v>
       </c>
       <c r="N65" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="O65" t="s">
         <v>9</v>
@@ -3967,22 +4007,22 @@
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="B66" t="s">
         <v>13</v>
       </c>
       <c r="C66" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="D66">
         <v>2261248051</v>
       </c>
       <c r="E66" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F66" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="G66">
         <v>100</v>
@@ -4006,7 +4046,7 @@
         <v>711</v>
       </c>
       <c r="N66" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="O66" t="s">
         <v>11</v>
@@ -4014,22 +4054,22 @@
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="B67" t="s">
         <v>13</v>
       </c>
       <c r="C67" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="D67">
         <v>3545957692</v>
       </c>
       <c r="E67" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F67" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="G67">
         <v>100</v>
@@ -4053,7 +4093,7 @@
         <v>711</v>
       </c>
       <c r="N67" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="O67" t="s">
         <v>11</v>
@@ -4061,66 +4101,66 @@
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="B68" t="s">
         <v>13</v>
       </c>
       <c r="C68" t="s">
-        <v>97</v>
+        <v>169</v>
       </c>
       <c r="D68">
         <v>2261286679</v>
       </c>
       <c r="E68" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F68" t="s">
-        <v>16</v>
-      </c>
-      <c r="G68" t="s">
-        <v>16</v>
+        <v>7</v>
+      </c>
+      <c r="G68">
+        <v>1000</v>
       </c>
       <c r="H68" t="s">
-        <v>16</v>
-      </c>
-      <c r="I68" t="s">
-        <v>16</v>
-      </c>
-      <c r="J68" t="s">
-        <v>16</v>
-      </c>
-      <c r="K68" t="s">
-        <v>16</v>
+        <v>10</v>
+      </c>
+      <c r="I68">
+        <v>57</v>
+      </c>
+      <c r="J68">
+        <v>5</v>
+      </c>
+      <c r="K68">
+        <v>0</v>
       </c>
       <c r="L68">
-        <v>83</v>
-      </c>
-      <c r="M68" t="s">
-        <v>16</v>
+        <v>82</v>
+      </c>
+      <c r="M68">
+        <v>658</v>
       </c>
       <c r="N68" t="s">
-        <v>16</v>
+        <v>170</v>
       </c>
       <c r="O68" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="B69" t="s">
         <v>13</v>
       </c>
       <c r="C69" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="D69">
         <v>2261467877</v>
       </c>
       <c r="E69" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F69" t="s">
         <v>7</v>
@@ -4147,7 +4187,7 @@
         <v>661</v>
       </c>
       <c r="N69" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="O69" t="s">
         <v>9</v>
@@ -4155,19 +4195,19 @@
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="B70" t="s">
         <v>13</v>
       </c>
       <c r="C70" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="D70">
-        <v>2261261115</v>
+        <v>2261338395</v>
       </c>
       <c r="E70" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F70" t="s">
         <v>16</v>
@@ -4188,7 +4228,7 @@
         <v>16</v>
       </c>
       <c r="L70">
-        <v>101</v>
+        <v>120</v>
       </c>
       <c r="M70" t="s">
         <v>16</v>
@@ -4202,19 +4242,19 @@
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="B71" t="s">
         <v>13</v>
       </c>
       <c r="C71" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="D71">
-        <v>2261338395</v>
+        <v>2261442019</v>
       </c>
       <c r="E71" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F71" t="s">
         <v>16</v>
@@ -4235,7 +4275,7 @@
         <v>16</v>
       </c>
       <c r="L71">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="M71" t="s">
         <v>16</v>
@@ -4249,140 +4289,140 @@
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="B72" t="s">
         <v>13</v>
       </c>
       <c r="C72" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="D72">
-        <v>2261442019</v>
+        <v>3537826900</v>
       </c>
       <c r="E72" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F72" t="s">
-        <v>16</v>
-      </c>
-      <c r="G72" t="s">
-        <v>16</v>
+        <v>7</v>
+      </c>
+      <c r="G72">
+        <v>1000</v>
       </c>
       <c r="H72" t="s">
-        <v>16</v>
-      </c>
-      <c r="I72" t="s">
-        <v>16</v>
-      </c>
-      <c r="J72" t="s">
-        <v>16</v>
-      </c>
-      <c r="K72" t="s">
-        <v>16</v>
+        <v>10</v>
+      </c>
+      <c r="I72">
+        <v>669</v>
+      </c>
+      <c r="J72">
+        <v>6</v>
+      </c>
+      <c r="K72">
+        <v>0</v>
       </c>
       <c r="L72">
-        <v>106</v>
-      </c>
-      <c r="M72" t="s">
-        <v>16</v>
+        <v>113</v>
+      </c>
+      <c r="M72">
+        <v>674</v>
       </c>
       <c r="N72" t="s">
-        <v>16</v>
+        <v>148</v>
       </c>
       <c r="O72" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="B73" t="s">
         <v>13</v>
       </c>
       <c r="C73" t="s">
-        <v>102</v>
+        <v>24</v>
       </c>
       <c r="D73">
-        <v>3537826900</v>
+        <v>2662179544</v>
       </c>
       <c r="E73" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F73" t="s">
-        <v>7</v>
+        <v>149</v>
       </c>
       <c r="G73">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="H73" t="s">
         <v>10</v>
       </c>
       <c r="I73">
-        <v>669</v>
+        <v>2474</v>
       </c>
       <c r="J73">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K73">
         <v>0</v>
       </c>
       <c r="L73">
-        <v>113</v>
+        <v>83</v>
       </c>
       <c r="M73">
-        <v>674</v>
+        <v>660</v>
       </c>
       <c r="N73" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="O73" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="B74" t="s">
         <v>13</v>
       </c>
       <c r="C74" t="s">
-        <v>26</v>
+        <v>93</v>
       </c>
       <c r="D74">
-        <v>2662179544</v>
+        <v>1975274217</v>
       </c>
       <c r="E74" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F74" t="s">
-        <v>159</v>
-      </c>
-      <c r="G74">
-        <v>5000</v>
+        <v>16</v>
+      </c>
+      <c r="G74" t="s">
+        <v>16</v>
       </c>
       <c r="H74" t="s">
-        <v>10</v>
-      </c>
-      <c r="I74">
-        <v>2474</v>
-      </c>
-      <c r="J74">
-        <v>4</v>
-      </c>
-      <c r="K74">
-        <v>0</v>
+        <v>16</v>
+      </c>
+      <c r="I74" t="s">
+        <v>16</v>
+      </c>
+      <c r="J74" t="s">
+        <v>16</v>
+      </c>
+      <c r="K74" t="s">
+        <v>16</v>
       </c>
       <c r="L74">
-        <v>83</v>
-      </c>
-      <c r="M74">
-        <v>660</v>
+        <v>52</v>
+      </c>
+      <c r="M74" t="s">
+        <v>16</v>
       </c>
       <c r="N74" t="s">
-        <v>160</v>
+        <v>16</v>
       </c>
       <c r="O74" t="s">
         <v>11</v>
@@ -4390,19 +4430,19 @@
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="B75" t="s">
         <v>13</v>
       </c>
       <c r="C75" t="s">
-        <v>103</v>
+        <v>25</v>
       </c>
       <c r="D75">
-        <v>1975274217</v>
+        <v>2264056624</v>
       </c>
       <c r="E75" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F75" t="s">
         <v>16</v>
@@ -4423,7 +4463,7 @@
         <v>16</v>
       </c>
       <c r="L75">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="M75" t="s">
         <v>16</v>
@@ -4437,19 +4477,19 @@
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="B76" t="s">
         <v>13</v>
       </c>
       <c r="C76" t="s">
-        <v>27</v>
+        <v>94</v>
       </c>
       <c r="D76">
-        <v>2264056624</v>
+        <v>4783958938</v>
       </c>
       <c r="E76" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F76" t="s">
         <v>16</v>
@@ -4470,7 +4510,7 @@
         <v>16</v>
       </c>
       <c r="L76">
-        <v>58</v>
+        <v>119</v>
       </c>
       <c r="M76" t="s">
         <v>16</v>
@@ -4484,101 +4524,57 @@
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="B77" t="s">
         <v>13</v>
       </c>
       <c r="C77" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="D77">
-        <v>4783958938</v>
+        <v>5158476730</v>
       </c>
       <c r="E77" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F77" t="s">
-        <v>16</v>
-      </c>
-      <c r="G77" t="s">
-        <v>16</v>
+        <v>7</v>
+      </c>
+      <c r="G77">
+        <v>50</v>
       </c>
       <c r="H77" t="s">
-        <v>16</v>
-      </c>
-      <c r="I77" t="s">
-        <v>16</v>
-      </c>
-      <c r="J77" t="s">
-        <v>16</v>
-      </c>
-      <c r="K77" t="s">
-        <v>16</v>
+        <v>12</v>
+      </c>
+      <c r="I77">
+        <v>1</v>
+      </c>
+      <c r="J77">
+        <v>4</v>
+      </c>
+      <c r="K77">
+        <v>0</v>
       </c>
       <c r="L77">
-        <v>119</v>
-      </c>
-      <c r="M77" t="s">
-        <v>16</v>
+        <v>120</v>
+      </c>
+      <c r="M77">
+        <v>141</v>
       </c>
       <c r="N77" t="s">
-        <v>16</v>
+        <v>151</v>
       </c>
       <c r="O77" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A78" t="s">
-        <v>162</v>
-      </c>
-      <c r="B78" t="s">
-        <v>13</v>
-      </c>
-      <c r="C78" t="s">
-        <v>105</v>
-      </c>
-      <c r="D78">
-        <v>5158476730</v>
-      </c>
-      <c r="E78" t="s">
-        <v>34</v>
-      </c>
-      <c r="F78" t="s">
-        <v>7</v>
-      </c>
-      <c r="G78">
-        <v>50</v>
-      </c>
-      <c r="H78" t="s">
-        <v>12</v>
-      </c>
-      <c r="I78">
-        <v>1</v>
-      </c>
-      <c r="J78">
-        <v>4</v>
-      </c>
-      <c r="K78">
-        <v>0</v>
-      </c>
-      <c r="L78">
-        <v>120</v>
-      </c>
-      <c r="M78">
-        <v>141</v>
-      </c>
-      <c r="N78" t="s">
-        <v>161</v>
-      </c>
-      <c r="O78" t="s">
         <v>9</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="C1:D1">
-    <cfRule type="duplicateValues" dxfId="0" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="27"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C1:C49 C51:C52 C54:C77">
+    <cfRule type="duplicateValues" dxfId="0" priority="29"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
